--- a/Gaining Fate リメイク/Gaining Fate ユニットスキル検討.xlsx
+++ b/Gaining Fate リメイク/Gaining Fate ユニットスキル検討.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1f96fe8b85c11756/ドキュメント/Github/Gaining_Fate_v2.0/Gaining Fate リメイク/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="14_{A4A0B838-2BC4-4AED-9D7A-EC3C987358E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B78C3A9F-1E61-4E94-9651-EDF245D05C5B}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="14_{A4A0B838-2BC4-4AED-9D7A-EC3C987358E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FC7B97B-F82F-4A26-8968-36FC6EB85690}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E75613F6-E52B-4491-838D-1E8247A3798F}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="109">
   <si>
     <t>Gaining Fate ユニットスキル検討</t>
     <rPh sb="20" eb="22">
@@ -964,6 +964,26 @@
     </rPh>
     <rPh sb="10" eb="12">
       <t>イガイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>二重人格</t>
+    <rPh sb="0" eb="4">
+      <t>ニジュウジンカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>下馬時、感情属性が変化する。</t>
+    <rPh sb="0" eb="3">
+      <t>ゲバジ</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>カンジョウゾクセイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヘンカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1474,25 +1494,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C247BC1C-AAE2-45DD-B88D-7E2DD6802E57}">
   <dimension ref="B2:I33"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="3.375" customWidth="1"/>
-    <col min="2" max="2" width="3.875" customWidth="1"/>
-    <col min="3" max="3" width="5.25" customWidth="1"/>
+    <col min="1" max="1" width="3.3984375" customWidth="1"/>
+    <col min="2" max="2" width="3.8984375" customWidth="1"/>
+    <col min="3" max="3" width="5.19921875" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.59765625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="67.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.5" customWidth="1"/>
-    <col min="8" max="8" width="13.25" customWidth="1"/>
-    <col min="9" max="9" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.19921875" customWidth="1"/>
+    <col min="9" max="9" width="14.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.45">
       <c r="D4" s="11" t="s">
         <v>80</v>
       </c>
@@ -1506,7 +1526,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.45">
       <c r="C5" s="5" t="s">
         <v>1</v>
       </c>
@@ -1522,7 +1542,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.45">
       <c r="C6" s="6" t="s">
         <v>99</v>
       </c>
@@ -1542,7 +1562,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.45">
       <c r="C7" s="6"/>
       <c r="D7" s="4" t="s">
         <v>4</v>
@@ -1560,7 +1580,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.45">
       <c r="C8" s="6"/>
       <c r="D8" s="4" t="s">
         <v>5</v>
@@ -1578,7 +1598,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.45">
       <c r="C9" s="6"/>
       <c r="D9" s="4" t="s">
         <v>6</v>
@@ -1596,7 +1616,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.45">
       <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
         <v>8</v>
@@ -1614,7 +1634,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.45">
       <c r="C11" s="6"/>
       <c r="D11" s="4" t="s">
         <v>7</v>
@@ -1632,7 +1652,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.45">
       <c r="C12" s="6"/>
       <c r="D12" s="4" t="s">
         <v>9</v>
@@ -1650,7 +1670,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.45">
       <c r="C13" s="6"/>
       <c r="D13" s="4" t="s">
         <v>10</v>
@@ -1668,7 +1688,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.45">
       <c r="C14" s="6"/>
       <c r="D14" s="4" t="s">
         <v>11</v>
@@ -1686,7 +1706,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.45">
       <c r="C15" s="6"/>
       <c r="D15" s="4" t="s">
         <v>12</v>
@@ -1704,7 +1724,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:9" x14ac:dyDescent="0.45">
       <c r="C16" s="6"/>
       <c r="D16" s="4" t="s">
         <v>13</v>
@@ -1722,7 +1742,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:9" x14ac:dyDescent="0.45">
       <c r="C17" s="6"/>
       <c r="D17" s="4" t="s">
         <v>14</v>
@@ -1740,7 +1760,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:9" x14ac:dyDescent="0.45">
       <c r="C18" s="6"/>
       <c r="D18" s="4" t="s">
         <v>15</v>
@@ -1754,7 +1774,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:9" x14ac:dyDescent="0.45">
       <c r="C19" s="6"/>
       <c r="D19" s="4" t="s">
         <v>16</v>
@@ -1772,7 +1792,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="3:9" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:9" x14ac:dyDescent="0.45">
       <c r="C20" s="6"/>
       <c r="D20" s="4" t="s">
         <v>17</v>
@@ -1790,7 +1810,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="21" spans="3:9" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:9" x14ac:dyDescent="0.45">
       <c r="C21" s="7"/>
       <c r="D21" s="4" t="s">
         <v>82</v>
@@ -1805,7 +1825,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="3:9" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:9" x14ac:dyDescent="0.45">
       <c r="C22" s="8" t="s">
         <v>34</v>
       </c>
@@ -1822,7 +1842,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="3:9" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:9" x14ac:dyDescent="0.45">
       <c r="C23" s="8"/>
       <c r="D23" s="3" t="s">
         <v>36</v>
@@ -1837,7 +1857,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="3:9" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:9" x14ac:dyDescent="0.45">
       <c r="C24" s="8"/>
       <c r="D24" s="3" t="s">
         <v>37</v>
@@ -1852,7 +1872,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="3:9" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:9" x14ac:dyDescent="0.45">
       <c r="C25" s="8"/>
       <c r="D25" s="3" t="s">
         <v>38</v>
@@ -1867,7 +1887,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="3:9" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:9" x14ac:dyDescent="0.45">
       <c r="C26" s="8"/>
       <c r="D26" s="3" t="s">
         <v>39</v>
@@ -1882,7 +1902,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="27" spans="3:9" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:9" x14ac:dyDescent="0.45">
       <c r="C27" s="8"/>
       <c r="D27" s="3" t="s">
         <v>40</v>
@@ -1897,7 +1917,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="3:9" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:9" x14ac:dyDescent="0.45">
       <c r="C28" s="8"/>
       <c r="D28" s="3" t="s">
         <v>41</v>
@@ -1912,7 +1932,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="3:9" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:9" x14ac:dyDescent="0.45">
       <c r="C29" s="8"/>
       <c r="D29" s="3" t="s">
         <v>42</v>
@@ -1927,7 +1947,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="3:9" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:9" x14ac:dyDescent="0.45">
       <c r="C30" s="8"/>
       <c r="D30" s="3" t="s">
         <v>43</v>
@@ -1942,16 +1962,22 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="3:9" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:9" x14ac:dyDescent="0.45">
       <c r="C31" s="8"/>
       <c r="D31" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-    </row>
-    <row r="32" spans="3:9" x14ac:dyDescent="0.4">
+      <c r="E31" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="3:9" x14ac:dyDescent="0.45">
       <c r="C32" s="9"/>
       <c r="D32" s="3" t="s">
         <v>45</v>
@@ -1962,7 +1988,7 @@
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
     </row>
-    <row r="33" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C33" s="10" t="s">
         <v>78</v>
       </c>

--- a/Gaining Fate リメイク/Gaining Fate ユニットスキル検討.xlsx
+++ b/Gaining Fate リメイク/Gaining Fate ユニットスキル検討.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1f96fe8b85c11756/ドキュメント/Github/Gaining_Fate_v2.0/Gaining Fate リメイク/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="14_{A4A0B838-2BC4-4AED-9D7A-EC3C987358E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FC7B97B-F82F-4A26-8968-36FC6EB85690}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="14_{A4A0B838-2BC4-4AED-9D7A-EC3C987358E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69D462B7-151F-495E-8BD7-D1BE9B334F4F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E75613F6-E52B-4491-838D-1E8247A3798F}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="110">
   <si>
     <t>Gaining Fate ユニットスキル検討</t>
     <rPh sb="20" eb="22">
@@ -602,13 +602,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>暴走</t>
-    <rPh sb="0" eb="2">
-      <t>ボウソウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>同盟</t>
     <rPh sb="0" eb="2">
       <t>ドウメイ</t>
@@ -984,6 +977,32 @@
     </rPh>
     <rPh sb="9" eb="11">
       <t>ヘンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>嫉妬</t>
+    <rPh sb="0" eb="2">
+      <t>シット</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自分以外の感情属性を持っているユニットに対し、必殺率+20%</t>
+    <rPh sb="0" eb="4">
+      <t>ジブンイガイ</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>カンジョウゾクセイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>ヒッサツリツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1514,7 +1533,7 @@
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.45">
       <c r="D4" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>18</v>
@@ -1544,19 +1563,19 @@
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.45">
       <c r="C6" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>21</v>
@@ -1595,7 +1614,7 @@
         <v>25</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.45">
@@ -1613,7 +1632,7 @@
         <v>28</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.45">
@@ -1622,10 +1641,10 @@
         <v>8</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>24</v>
@@ -1643,7 +1662,7 @@
         <v>48</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>25</v>
@@ -1676,10 +1695,10 @@
         <v>10</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>22</v>
@@ -1718,7 +1737,7 @@
         <v>73</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>28</v>
@@ -1736,7 +1755,7 @@
         <v>74</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>29</v>
@@ -1751,7 +1770,7 @@
         <v>56</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>22</v>
@@ -1807,19 +1826,19 @@
         <v>27</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="3:9" x14ac:dyDescent="0.45">
       <c r="C21" s="7"/>
       <c r="D21" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E21" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>21</v>
@@ -1836,10 +1855,10 @@
         <v>58</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="3:9" x14ac:dyDescent="0.45">
@@ -1899,7 +1918,7 @@
         <v>61</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="3:9" x14ac:dyDescent="0.45">
@@ -1908,13 +1927,13 @@
         <v>40</v>
       </c>
       <c r="E27" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="G27" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="3:9" x14ac:dyDescent="0.45">
@@ -1923,10 +1942,10 @@
         <v>41</v>
       </c>
       <c r="E28" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>84</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>22</v>
@@ -1938,10 +1957,10 @@
         <v>42</v>
       </c>
       <c r="E29" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>94</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>23</v>
@@ -1953,10 +1972,10 @@
         <v>43</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>29</v>
@@ -1968,13 +1987,13 @@
         <v>44</v>
       </c>
       <c r="E31" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="F31" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="G31" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="3:9" x14ac:dyDescent="0.45">
@@ -1983,23 +2002,27 @@
         <v>45</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
+        <v>108</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="33" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C33" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="F33" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>24</v>
